--- a/DW/Diseño DW.xlsx
+++ b/DW/Diseño DW.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uhispano-my.sharepoint.com/personal/anthony_villalobos0872_uhispano_ac_cr/Documents/Universidad/VII Cuatri/BD/Proyecto/DW/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="8_{7B331317-0294-4D6A-A2AB-5A9A270C473C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2D86706-A4A6-431E-AA09-50A9EE86E8DB}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="8_{7B331317-0294-4D6A-A2AB-5A9A270C473C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31B4CA53-E7D8-4A4A-9007-2156E02BC628}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{4FD1E55B-BC30-4A39-93B9-D1E5AFCC1232}"/>
+    <workbookView xWindow="29760" yWindow="960" windowWidth="21600" windowHeight="11235" activeTab="2" xr2:uid="{4FD1E55B-BC30-4A39-93B9-D1E5AFCC1232}"/>
   </bookViews>
   <sheets>
     <sheet name="ER" sheetId="1" r:id="rId1"/>
-    <sheet name="Hechos" sheetId="2" r:id="rId2"/>
-    <sheet name="Dimensiones" sheetId="3" r:id="rId3"/>
+    <sheet name="Hechos" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Hechos2" sheetId="4" r:id="rId3"/>
+    <sheet name="Dimensiones" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="41">
   <si>
     <t>EMPLEADO</t>
   </si>
@@ -430,7 +431,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -441,6 +442,69 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -454,66 +518,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -548,8 +552,8 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>15525</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="9" name="Entrada de lápiz 8">
@@ -568,7 +572,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="9" name="Entrada de lápiz 8">
@@ -609,12 +613,12 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>505695</xdr:colOff>
+      <xdr:colOff>511410</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>38250</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="12" name="Entrada de lápiz 11">
@@ -633,7 +637,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="12" name="Entrada de lápiz 11">
@@ -674,12 +678,12 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>693360</xdr:colOff>
+      <xdr:colOff>702885</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>59055</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="22" name="Entrada de lápiz 21">
@@ -698,7 +702,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="22" name="Entrada de lápiz 21">
@@ -743,8 +747,8 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>54045</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="26" name="Entrada de lápiz 25">
@@ -763,7 +767,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="26" name="Entrada de lápiz 25">
@@ -804,12 +808,12 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>560670</xdr:colOff>
+      <xdr:colOff>562575</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>29385</xdr:rowOff>
+      <xdr:rowOff>17955</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="27" name="Entrada de lápiz 26">
@@ -828,7 +832,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="27" name="Entrada de lápiz 26">
@@ -869,12 +873,12 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>11865</xdr:colOff>
+      <xdr:colOff>19485</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>97695</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="32" name="Entrada de lápiz 31">
@@ -893,7 +897,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="32" name="Entrada de lápiz 31">
@@ -951,8 +955,8 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1476 5618 24575,'1'-58'-191,"-2"-1"0,-3 1-1,-17-82 1,-42-168 191,19 96-155,27 121 151,3-8 4,10 62 0,-16-67 0,5 38 276,2 0 0,-5-119 0,12 105-180,-20-79-96,17 104 0,2 8 0,-4-88 0,10 114 0,-1 1 0,-8-35 0,-3-34 0,13 82-90,0-7-165,-1 0 0,0 0 0,-1 0 0,-4-17 0,0 14-6571</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1486.95">0 3248 24575,'0'-8'0,"1"0"0,0 1 0,1-1 0,0 0 0,0 1 0,0-1 0,1 1 0,0-1 0,6-9 0,45-62 0,-7 9 0,-31 41 0,150-247 0,-123 209-10,46-95 0,-59 104-94,131-244-514,-126 231 618,33-59 0,-55 103 144,0 0 0,9-30 0,16-34 166,-25 61-310,-1-2 0,-1 1 0,8-41 0,16-48 0,-23 82 0,13-68 0,-16 62 0,14-42 0,65-144 0,-48 107 0,18-24 0,-43 101 0,2 1 0,30-52 0,-31 63 0,0 0 0,-3 0 0,11-41 0,18-45 0,-31 89 0,13-63 0,-13 48 0,-11 56 0,1 0 0,0 1 0,0-1 0,1 0 0,6 18 0,4 31 0,-7-28 0,1-1 0,14 43 0,-8-34 0,11 65 0,-16-69 0,0-1 0,23 58 0,-13-45 0,13 55 0,3 8 0,204 448-961,-216-511 953,73 148-191,-14-60 199,-47-75 365,54 72 0,-28-47-101,16 26-177,129 144 0,-154-196-87,34 37 0,-72-83 2,-2 0 0,16 25 0,-8-12-1373,-9-12-5455</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1482 5609 24575,'1'-58'-191,"-2"-1"0,-3 1-1,-17-81 1,-43-169 191,21 97-155,26 120 151,3-8 4,10 62 0,-16-67 0,5 38 276,1 0 0,-4-119 0,12 106-180,-20-80-96,17 104 0,2 8 0,-4-88 0,10 115 0,-1-1 0,-8-34 0,-3-34 0,13 83-90,0-8-165,-1 0 0,0 0 0,-1-1 0,-4-15 0,0 13-6571</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1486.95">0 3243 24575,'0'-8'0,"1"0"0,0 1 0,1-2 0,0 1 0,0 2 0,0-2 0,1 1 0,0-1 0,6-9 0,45-62 0,-6 9 0,-32 41 0,150-246 0,-123 208-10,47-95 0,-60 104-94,132-243-514,-127 230 618,33-59 0,-55 103 144,0 0 0,10-30 0,14-34 166,-24 61-310,-1-2 0,-1 2 0,8-43 0,16-46 0,-23 81 0,14-68 0,-17 62 0,14-42 0,65-144 0,-47 108 0,17-25 0,-43 101 0,2 2 0,30-53 0,-31 62 0,1 1 0,-4 1 0,11-42 0,18-45 0,-32 88 0,14-62 0,-13 49 0,-11 55 0,1 0 0,0 1 0,0-1 0,1-1 0,6 20 0,4 29 0,-7-26 0,1-2 0,15 43 0,-9-35 0,11 66 0,-16-69 0,0-1 0,23 58 0,-13-45 0,13 55 0,4 7 0,204 449-961,-217-511 953,73 147-191,-14-59 199,-47-75 365,55 72 0,-29-47-101,17 25-177,128 146 0,-154-198-87,35 38 0,-73-83 2,-2-1 0,16 27 0,-8-13-1373,-9-12-5455</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -979,8 +983,8 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 616 24575,'1'-1'0,"-1"0"0,1 0 0,-1-1 0,1 1 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 1 0,1-1 0,-1 0 0,2 0 0,33-13 0,-27 11 0,78-29 0,97-41 0,-108 44-1365,-60 23-5461</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="793.49">74 135 24575,'0'-1'0,"0"0"0,1 0 0,-1 0 0,0 0 0,1 0 0,-1 0 0,1 0 0,0 1 0,-1-1 0,1 0 0,-1 0 0,1 1 0,0-1 0,0 0 0,-1 1 0,1-1 0,0 0 0,0 1 0,0-1 0,0 1 0,0 0 0,0-1 0,0 1 0,0 0 0,1-1 0,34-8 0,-19 5 0,19-8 0,-7 1 0,1 2 0,41-8 0,-15 7 0,-27 4 0,1 1 0,41 0 0,-32 3 0,52-9 0,-53 5 0,58-1 0,33 5 0,140 5 0,-255-1 0,0 0 0,0 1 0,26 9 0,-36-11 0,0 1 0,-1 0 0,1 0 0,0 0 0,0 0 0,-1 1 0,6 4 0,-8-5 0,0-1 0,0 0 0,0 0 0,0 0 0,0 1 0,0-1 0,-1 0 0,1 1 0,0-1 0,-1 0 0,0 1 0,1-1 0,-1 1 0,0-1 0,1 1 0,-1-1 0,0 1 0,0-1 0,0 1 0,0-1 0,-1 1 0,1 1 0,-1-1 0,0 0 0,0-1 0,0 1 0,0 0 0,-1 0 0,1-1 0,-1 1 0,1 0 0,-1-1 0,1 0 0,-1 1 0,0-1 0,1 0 0,-1 0 0,0 0 0,0 0 0,0 0 0,-3 1 0,-46 14 0,27-9 0,11-2 0,1 1 0,0 0 0,1 1 0,-1 1 0,2 0 0,-1 0 0,1 1 0,0 1 0,1-1 0,0 1 0,0 1 0,1 0 0,1 0 0,0 1 0,0-1 0,1 2 0,-8 23 0,4-3 0,-11 68 0,11-60-1365,4-24-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 628 24575,'1'-1'0,"-1"0"0,1 0 0,-1-1 0,1 1 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 1 0,1-1 0,-1 0 0,3 0 0,33-14 0,-28 12 0,80-29 0,100-43 0,-110 46-1365,-63 23-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="793.49">76 138 24575,'0'-1'0,"0"0"0,1 0 0,-1 0 0,0 0 0,1-1 0,-1 1 0,1 0 0,0 1 0,-1-1 0,1 0 0,-1 0 0,1 1 0,0-1 0,0 0 0,-1 1 0,1-1 0,0 0 0,0 1 0,0-1 0,0 1 0,0 0 0,0-1 0,1 1 0,-1 0 0,1-1 0,35-8 0,-20 5 0,20-8 0,-7 1 0,1 1 0,42-7 0,-16 7 0,-27 4 0,1 1 0,42 0 0,-33 3 0,54-10 0,-55 6 0,59-1 0,35 5 0,143 5 0,-261-1 0,-1 0 0,1 1 0,26 9 0,-37-11 0,0 1 0,-1 1 0,1-1 0,0 0 0,0 0 0,-1 1 0,7 4 0,-9-5 0,0-1 0,0 0 0,0 0 0,0 0 0,0 1 0,0-1 0,-1 0 0,1 1 0,0-1 0,-1 0 0,0 1 0,1-1 0,-1 1 0,0-1 0,1 1 0,-1-1 0,0 1 0,0-1 0,0 1 0,0-1 0,-1 1 0,1 2 0,-1-2 0,0 0 0,0-1 0,0 1 0,0 0 0,-1 0 0,1-1 0,-1 1 0,1 0 0,-1-1 0,1 0 0,-2 1 0,1-1 0,1 0 0,-1 0 0,0 0 0,0 0 0,0 0 0,-3 1 0,-47 14 0,27-9 0,12-1 0,0 0 0,1 0 0,1 1 0,-2 1 0,3 0 0,-1 0 0,0 2 0,1 0 0,1-1 0,0 1 0,-1 1 0,2 1 0,1-1 0,0 1 0,0-1 0,0 3 0,-7 22 0,4-2 0,-12 69 0,12-61-1365,4-25-5461</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -1007,16 +1011,16 @@
       <inkml:brushProperty name="height" value="0.035" units="cm"/>
     </inkml:brush>
   </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1298 1353 24575,'0'32'0,"-6"55"0,-35 82 0,-31 104 0,-83 337-3441,-124 466-6967,203-814 10255,-9 31 3526,23-91-2048,-27 110 1023,14-43-2470,4-18-170,23-70 292,-7 31 0,-11 58 1187,52-203-981,-41 163 129,47-192 156,1 0 0,-3 56 0,-3 23 1067,7-64-818,2 0 0,3 76 0,2-63-349,-1-63-390,0-1 0,0 1-1,1 0 1,-1-1-1,0 1 1,1 0 0,0-1-1,-1 1 1,1-1 0,0 1-1,0-1 1,1 1 0,-1-1-1,0 1 1,1-1 0,0 0-1,-1 0 1,1 0 0,0 0-1,0 0 1,0 0-1,0-1 1,0 1 0,1-1-1,-1 1 1,0-1 0,1 0-1,-1 0 1,1 0 0,3 1-1,7 1-19,1-1 0,-1 0 0,1-1 1,0-1-1,14-1 0,25 2-617,206 39-1199,-66 2-190,-75-14 1048,377 105-1215,-113-25 684,141 6-507,-396-87 2015,163 25 0,-44-17-314,174 13-385,40-22 1060,254 4 338,116-16-681,-351-6 489,-97-5-312,-192 10 779,57 1-418,-193-15 863,107 5 2597,-158-4-3973,0 0 1,0 1 0,0-1-1,0-1 1,0 1 0,0 0-1,0-1 1,0 0 0,0 0-1,0 1 1,0-2 0,0 1-1,-1 0 1,1-1 0,0 1-1,-1-1 1,1 0 0,-1 0-1,0 0 1,1 0 0,-1 0-1,0 0 1,0-1 0,0 1-1,-1-1 1,1 1 0,-1-1-1,1 0 1,-1 1 0,0-1-1,0 0 1,0 0 0,1-5-1,2-10 169,-2-1 0,0 1 0,0-1 0,-3-27 0,1 22-161,14-319-2010,0 39-2405,-15-156 3594,-2 163 751,3-2709-1063,-13 2746 1482,-1 9-85,1-74-446,0-10 301,13 264 538,-1-63-495,19-139 1,8-39 3957,-14 166-3242,-11 96-648,3 0 0,19-86 0,20-94 51,-19 80-342,-15 99 167,-5 24 53,2 0-1,0 0 0,15-40 0,-13 55-209,-5 20 0,-7 22 0,-3-7 0,-2-1 0,0 0 0,-2 0 0,0-1 0,-1-1 0,-1 1 0,-1-2 0,-1 0 0,0-1 0,-30 26 0,-8 1-134,-2-3-1,-2-2 1,-2-3 0,-2-2-1,-81 34 1,-109 35 134,98-42-774,-223 60 1,338-111 957,-241 60-1164,49-33-1784,73-15 2654,44-9-657,0-5 0,-185-9 0,132-3 370,-1853 3 9118,2011 0-8721,0 1 0,0 0 0,1 0 0,-1 1 0,0 0 0,1 0 0,0 1 0,-1-1 0,1 2 0,0-1 0,0 1 0,1 0 0,-10 8 0,-4 5 0,1 2 0,-29 34 0,-10 10 0,-90 96 0,57-59 0,-239 236 0,318-325 0,0-1 0,0 0 0,-1 0 0,-15 7 0,21-13 0,0 0 0,1-1 0,-1 0 0,-1 0 0,1-1 0,0 0 0,-1 0 0,1 0 0,-1-1 0,-10 0 0,6-3 0,-1-1 0,1-1 0,0 0 0,0-1 0,0 0 0,1 0 0,0-1 0,0-1 0,0 0 0,-16-15 0,-43-24 0,-1 12-1365,53 28-5461</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="851.15">2123 2914 24575,'2'83'0,"1"-53"0,-2-1 0,-1 1 0,-2 0 0,0 0 0,-2-1 0,-15 55 0,5-38 0,2 0 0,-8 61 0,2-9 0,-51 267 0,65-337 0,-2 16 0,-1 0 0,-15 45 0,11-48 0,-9 80 0,11-59 0,3 36-1365,6-75-5461</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1282.75">2802 2824 24575,'0'45'0,"-2"-1"0,-2 1 0,-16 75 0,20-119 1,-80 396-677,73-354 676,-14 48 0,-5 26 0,-10 33-41,23-103 343,-13 82 0,19-86-262,-2 1 1,-15 41-1,10-39-44,-10 68-1,2-24-1360,17-72-5461</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1702.35">2034 4094 24575,'17'-2'0,"-1"0"0,1 0 0,22-7 0,1-1 0,6 1 0,-18 2 0,0 2 0,1 1 0,29 0 0,-3 3 0,92-13 0,-71 1 0,82-28 0,-54 16 38,-67 18-506,0-3 1,52-19-1,-72 21-6358</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="39812.33">4938 2527 24575,'0'4'0,"0"0"0,0 0 0,0 0 0,-1 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,-1-1 0,0 1 0,0-1 0,0 1 0,0-1 0,-1 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,0-1 0,0 1 0,0-1 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1-1 0,0 1 0,0-1 0,-6 1 0,-182 72 0,86-31 0,49-20 0,20-8 0,-75 22 0,96-33 0,1 2 0,0-1 0,-19 12 0,-25 9 0,18-9 0,1 1 0,1 2 0,0 2 0,2 2 0,1 1 0,1 1 0,1 3 0,1 0 0,-32 39 0,44-43-39,1 1 1,1 0-1,1 2 0,1 0 0,2 1 0,1 1 0,1 0 1,2 1-1,-13 51 0,12-16-58,2 0 0,3 1 0,3 113 0,3-120 97,0-36 0,0-1 0,2 0 0,0 1 0,2-1 0,0 0 0,2 0 0,12 37 0,8 2 58,-5-11 155,31 55 1,-43-91-182,0-2 0,1 0 1,1 0-1,0 0 1,1-1-1,0-1 0,1 0 1,19 15-1,-19-19-32,-1-1 0,2 0 0,-1 0 0,0-1 0,1-1 0,0 0 0,0-1 0,0-1 0,1 0 0,-1 0 0,0-1 0,16-1 0,-12-1 0,-1-1 0,0 0 0,0 0 0,0-2 0,0 0 0,0-1 0,-1-1 0,0 0 0,23-13 0,-19 7 0,101-67 0,101-75 0,-97 51 0,-77 65 0,-2-3 0,-2-1 0,-2-3 0,59-81 0,-90 109 0,0 0 0,-1-1 0,-1 0 0,-1 0 0,0-1 0,-2 0 0,0 0 0,-1 0 0,-1-1 0,1-36 0,-4 49 7,0 1 0,-1-1-1,0 1 1,-1 0 0,1-1-1,-1 1 1,0 0-1,-1 0 1,0 0 0,0 1-1,0-1 1,0 0 0,-1 1-1,0 0 1,0 0 0,0 0-1,-10-7 1,2 2-219,0 1 0,-1 1 0,0 0-1,-1 0 1,0 2 0,-20-8 0,16 8-6614</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="40572.42">4431 2496 24575,'-21'55'0,"-31"178"-420,10-50-140,13 12-462,8-40 299,-1 36 723,15-115 0,-17 85 0,-23 101 0,19-105-282,4-36-88,-21 76 143,31-142 229,-33 78 2738,18 21-1878,9-68-2227,17-67-5461</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="41085.88">3658 3247 24575,'5'2'0,"0"-1"0,-1 0 0,1 1 0,0 0 0,-1 0 0,1 0 0,-1 1 0,6 4 0,11 5 0,156 66 0,-155-69 0,0-1 0,1-1 0,0-1 0,0-1 0,30 2 0,119-1 0,-145-9 0,0-1 0,0-1 0,0-1 0,-1-1 0,0-2 0,37-17 0,57-17 0,-110 39 0,1-1 0,-1 1 0,0-2 0,0 1 0,9-8 0,35-18 0,52-21-1365,-91 45-5461</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="41601.46">4632 2321 24575,'-6'0'0,"1"1"0,-1-1 0,0 1 0,1 0 0,-1 0 0,1 1 0,0-1 0,0 1 0,-1 0 0,1 1 0,0 0 0,1-1 0,-1 1 0,0 1 0,1-1 0,0 1 0,-1 0 0,2 0 0,-6 6 0,-3 6 0,1 1 0,1 1 0,1 0 0,-8 21 0,14-34 0,-18 43-54,-126 325-532,95-241 446,34-90 146,-22 72 0,-50 212-6,79-292 0,-3 9 0,-10 59 0,13-52-13,7-31 231,0-1 0,-2 27-1,-8 44-77,9-67-144,1 1 0,-1 27 0,5-46 4,-1 10 0,1 0 0,0 0 0,1 0 0,0-1 0,6 22 0,-6-31 0,1 0 0,0 0 0,0 0 0,0 0 0,0-1 0,1 1 0,-1 0 0,1-1 0,0 0 0,0 0 0,0 0 0,0 0 0,1 0 0,-1 0 0,1-1 0,0 0 0,0 1 0,0-2 0,0 1 0,0 0 0,7 1 0,4 1 0,-1 0 0,1-2 0,0 1 0,0-2 0,0 0 0,0-1 0,1-1 0,-1 0 0,0-1 0,-1 0 0,24-7 0,-15 1 0,0-1 0,-1-1 0,0-1 0,-1 0 0,0-2 0,27-21 0,117-104 0,-134 108-113,100-105-1139,-118 119-5574</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="42310.97">3938 3607 24575,'-13'16'0,"-4"2"0,17-17 0,0-1 0,-1 1 0,1-1 0,0 0 0,0 1 0,0-1 0,0 1 0,0-1 0,0 1 0,1-1 0,-1 0 0,0 1 0,0-1 0,0 1 0,0-1 0,0 1 0,1-1 0,-1 0 0,0 1 0,0-1 0,0 0 0,1 1 0,-1-1 0,0 0 0,1 1 0,-1-1 0,0 0 0,1 0 0,-1 1 0,0-1 0,1 0 0,-1 0 0,1 0 0,-1 1 0,0-1 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,0 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,0 0 0,5 0 0,1 0 0,0 0 0,0 0 0,0-1 0,0 0 0,0-1 0,-1 1 0,1-1 0,-1 0 0,10-5 0,67-37 0,-64 33 0,91-50 0,217-136 0,-10-40 0,-302 226 0,-7 6 0,0-1 0,0-1 0,0 1 0,0-1 0,-1 0 0,0-1 0,10-15 0,-17 23 0,0 0 0,1 0 0,-1 0 0,0-1 0,0 1 0,0 0 0,0 0 0,0 0 0,0-1 0,0 1 0,0 0 0,0 0 0,0-1 0,0 1 0,0 0 0,0 0 0,0-1 0,0 1 0,0 0 0,0 0 0,0 0 0,0-1 0,0 1 0,0 0 0,0 0 0,0 0 0,0-1 0,-1 1 0,1 0 0,0 0 0,0 0 0,0-1 0,0 1 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,0-1 0,-1 1 0,1 0 0,0 0 0,0 0 0,-1 0 0,-13 1 0,-14 9 0,-64 41-627,3 5-1,3 3 1,-100 88-1,107-75 529,21-20-144,-94 109 0,42-7 243,90-125 85,6-9 206,1 0 1,1 0 0,1 2 0,1-1-1,0 1 1,-9 34 0,15-18 504,4-37-790,0-1 0,0 0 0,0 0-1,0 1 1,0-1 0,0 0 0,1 0 0,-1 1-1,0-1 1,0 0 0,0 0 0,0 1-1,1-1 1,-1 0 0,0 0 0,0 0 0,1 0-1,-1 1 1,0-1 0,0 0 0,1 0-1,-1 0 1,0 0 0,0 0 0,1 0 0,-1 0-1,0 0 1,0 0 0,1 0 0,-1 0-1,0 0 1,1 0 0,-1 0 0,0 0 0,0 0-1,1 0 1,-1 0 0,21-13-54,113-111 48,-85 76 0,84-66 0,1 3 0,-90 65 0,-37 37 0,1 0 0,0 1 0,16-14 0,-22 21 0,0 0 0,0-1 0,-1 1 0,1 0 0,0 0 0,-1-1 0,1 1 0,-1-1 0,0 0 0,1 1 0,-1-1 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,-1 0 0,1 0 0,0-4 0,-1 4 0,-1 1 0,1-1 0,0 1 0,-1-1 0,0 1 0,1 0 0,-1-1 0,0 1 0,0 0 0,0-1 0,0 1 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,-3-1 0,-11-4 0,0-1 0,-1 2 0,0 0 0,-18-3 0,10 2 0,-29-11 0,37 11 0,0 0 0,0 2 0,0 0 0,-31-3 0,-43-6 0,64 8 0,1 1 0,-32-1 0,19 3 0,-49-9 0,49 5 0,-50-1 0,54 6 0,15 0 0,-1 1 0,-29 3 0,49-3 0,-1 1 0,1-1 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 1 0,0-1 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,-1 1 0,1-1 0,0 0 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 1 0,1-1 0,-1 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,1 0 0,-1 1 0,16 18 0,26 15 0,-24-26 0,0 0 0,0-2 0,1 0 0,0-1 0,0-1 0,0 0 0,26 0 0,144-4 0,-86-3 0,-36 1 0,-41 0 0,1 1 0,-1 2 0,1 0 0,33 7 0,-24 8-1365,-24-6-5461</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="43212.23">3531 2368 24575,'25'1'0,"1"1"0,0 1 0,-1 1 0,1 1 0,31 11 0,12 8-110,2-3 0,0-4 0,1-2 0,0-4 0,1-3 0,85-1 0,-136-7 110,-1-2 0,0 0 0,0-1 0,0-1 0,36-12 0,252-77 0,-16-9-9,-180 68-54,-99 30 182,0 1 1,0 1-1,1 0 0,-1 1 0,0 1 0,16 1 1,-29-1-120,-1 0 0,0 0 0,1 0 0,-1 0 0,0 0 1,1 0-1,-1 0 0,0 1 0,1-1 0,-1 0 0,0 0 1,1 0-1,-1 0 0,0 0 0,1 1 0,-1-1 1,0 0-1,0 0 0,1 1 0,-1-1 0,0 0 0,0 0 1,1 1-1,-1-1 0,0 0 0,0 1 0,0-1 0,0 0 1,1 0-1,-1 1 0,0-1 0,0 0 0,0 1 1,0-1-1,0 1 0,0-1 0,0 0 0,0 1 0,0-1 1,-9 18 0,-22 16-2,29-32 1,-81 76 0,-47 49 0,16-5 0,-93 111 0,139-147 141,35-46-404,1 1 0,2 1 1,-43 82-1,58-92 310,6-14 95,0 1 1,2-1-1,0 1 0,-8 37 1,11-32-65,-5 26-54,2 0 1,0 60-1,7-65-24,-1-23 0,0-1 0,2 1 0,1 0 0,0-1 0,2 0 0,7 26 0,-9-43 0,0 1 0,0-1 0,1 0 0,0 0 0,0 0 0,0-1 0,0 1 0,0-1 0,1 1 0,-1-1 0,1 0 0,0 0 0,0-1 0,0 1 0,0-1 0,1 0 0,-1 0 0,1 0 0,-1-1 0,1 1 0,-1-1 0,9 1 0,11 1 0,-1-1 0,1-1 0,32-3 0,-26 1 0,-18 1 0,-1-1 0,1 0 0,-1 0 0,1-2 0,-1 1 0,0-1 0,0-1 0,0 0 0,0-1 0,-1 0 0,0 0 0,19-14 0,-14 10 0,1 1 0,0 0 0,17-5 0,-21 8 0,0 1 0,0-1 0,0-1 0,-1 0 0,0-1 0,0 0 0,10-9 0,-78 45 0,5 6 0,-77 69 0,-21 14 0,27-45 0,75-47 0,-111 77 0,87-55 0,59-39 0,0 1 0,1 0 0,0 0 0,0 1 0,-12 16 0,22-25 0,0 0 0,1 0 0,-1 1 0,1-1 0,0 0 0,0 1 0,0-1 0,0 1 0,0-1 0,0 1 0,1 0 0,-1-1 0,1 1 0,0 0 0,-1-1 0,2 5 0,-1-5 0,1 0 0,0 0 0,0 0 0,0 0 0,1 0 0,-1 0 0,0 0 0,1 0 0,-1 0 0,1-1 0,0 1 0,-1-1 0,1 1 0,0-1 0,0 1 0,0-1 0,0 0 0,0 0 0,1 0 0,-1 0 0,0-1 0,4 2 0,17 4-1365,0-3-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">1303 1351 24575,'0'33'0,"-6"53"0,-35 83 0,-31 103 0,-85 338-3441,-122 464-6967,203-812 10255,-10 31 3526,24-92-2048,-27 111 1023,14-44-2470,3-17-170,24-70 292,-8 31 0,-10 57 1187,52-202-981,-41 163 129,47-192 156,1 0 0,-3 56 0,-3 23 1067,7-65-818,2 2 0,3 74 0,2-61-349,-1-65-390,0 0 0,0 1-1,1 0 1,-1-1-1,0 1 1,1 0 0,0-1-1,-1 1 1,1-1 0,0 1-1,0-1 1,1 1 0,-1-1-1,0 1 1,1-1 0,0 0-1,-1 0 1,1 0 0,0 0-1,0 0 1,0 0-1,0-1 1,0 1 0,1-1-1,-1 1 1,0-1 0,1 0-1,-1 0 1,1 0 0,3 1-1,7 1-19,1-1 0,-1 0 0,1-1 1,0-1-1,14-1 0,25 2-617,208 39-1199,-68 2-190,-74-14 1048,378 104-1215,-114-24 684,142 6-507,-398-86 2015,165 23 0,-46-15-314,176 11-385,39-21 1060,256 4 338,116-16-681,-352-6 489,-97-5-312,-194 10 779,58 1-418,-194-15 863,108 5 2597,-159-4-3973,0 0 1,0 1 0,0-1-1,0-1 1,0 1 0,0 0-1,0-1 1,0 0 0,0 0-1,0 1 1,0-2 0,0 1-1,-1 0 1,1-1 0,1 1-1,-2-1 1,1 0 0,-1 0-1,0 0 1,1 0 0,-1 0-1,0 0 1,0-1 0,0 1-1,-1-1 1,1 1 0,-1-1-1,1 0 1,-1 1 0,0-1-1,0 1 1,0-1 0,1-6-1,2-9 169,-2-1 0,0 1 0,0-1 0,-3-27 0,1 22-161,14-318-2010,0 38-2405,-15-155 3594,-2 162 751,3-2705-1063,-13 2742 1482,-1 10-85,1-75-446,0-9 301,13 262 538,-1-61-495,19-139 1,8-40 3957,-14 166-3242,-11 96-648,3 0 0,19-86 0,20-94 51,-19 81-342,-15 97 167,-5 26 53,2-1-1,0 0 0,15-40 0,-13 55-209,-5 20 0,-7 22 0,-3-7 0,-2-1 0,0 0 0,-2 0 0,0-2 0,-1 1 0,-1 0 0,-1-2 0,-1 0 0,0-2 0,-30 28 0,-8 0-134,-3-4-1,-1 0 1,-3-5 0,-1-1-1,-81 34 1,-110 35 134,99-42-774,-225 60 1,340-111 957,-242 59-1164,49-31-1784,73-16 2654,45-9-657,0-6 0,-187-8 0,134-3 370,-1861 3 9118,2019 0-8721,0 1 0,0 0 0,1 0 0,-1 1 0,0 0 0,1 0 0,0 1 0,-1-1 0,1 2 0,0-1 0,0 1 0,1 0 0,-10 9 0,-4 4 0,1 2 0,-29 33 0,-10 11 0,-91 96 0,57-59 0,-239 235 0,319-323 0,0-2 0,0 0 0,-1 0 0,-15 7 0,21-13 0,0 0 0,1-2 0,-1 1 0,-1 0 0,1-1 0,0 0 0,-1 0 0,1 0 0,-1-1 0,-10 0 0,6-3 0,-1-1 0,1-1 0,0 0 0,0 0 0,0-1 0,1 0 0,0-1 0,0-1 0,0 0 0,-16-15 0,-45-24 0,1 12-1365,53 28-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="851.15">2131 2911 24575,'2'82'0,"1"-52"0,-2-1 0,-1 1 0,-2-1 0,0 2 0,-2-2 0,-15 55 0,5-39 0,2 2 0,-8 60 0,2-10 0,-52 268 0,66-337 0,-2 15 0,-1 2 0,-15 44 0,11-49 0,-9 81 0,11-59 0,3 36-1365,6-75-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1282.75">2812 2820 24575,'0'45'0,"-2"0"0,-2-1 0,-16 76 0,20-119 1,-80 396-677,73-355 676,-14 49 0,-5 26 0,-10 32-41,23-101 343,-13 81 0,19-87-262,-2 3 1,-15 40-1,10-40-44,-10 69-1,2-24-1360,16-72-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1702.35">2042 4088 24575,'17'-2'0,"-1"0"0,1 0 0,22-7 0,1-1 0,6 2 0,-18 1 0,0 2 0,1 1 0,29 0 0,-3 3 0,94-13 0,-73 1 0,82-29 0,-53 18 38,-68 17-506,0-3 1,52-19-1,-72 21-6358</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="39812.33">4956 2524 24575,'0'4'0,"0"-1"0,0 1 0,0 0 0,-1 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,-1 0 0,0 0 0,0-1 0,0 1 0,0-1 0,-1 0 0,1 0 0,-1 0 0,0 0 0,0 0 0,0-1 0,0 1 0,0-1 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1-1 0,0 1 0,0-1 0,-6 1 0,-182 72 0,84-32 0,51-19 0,20-8 0,-75 23 0,96-35 0,1 3 0,0-1 0,-19 12 0,-25 9 0,18-9 0,0 2 0,2 0 0,0 3 0,2 2 0,1 1 0,1 1 0,1 3 0,1 0 0,-33 39 0,45-43-39,1 0 1,1 2-1,1 1 0,0 0 0,3 0 0,1 3 0,1-1 1,2 0-1,-13 53 0,12-18-58,2 1 0,3 1 0,3 113 0,3-120 97,0-36 0,0-2 0,2 2 0,0 0 0,2-1 0,0-1 0,2 1 0,12 38 0,8 0 58,-5-10 155,32 55 1,-44-91-182,0-2 0,1 0 1,1 0-1,0 1 1,1-3-1,0 0 0,1 0 1,19 15-1,-19-19-32,0-1 0,1 0 0,-1 0 0,0-1 0,1-1 0,0 0 0,0-1 0,0-1 0,1 0 0,-1 0 0,0-1 0,16-1 0,-12-1 0,-1-1 0,0 0 0,0 0 0,0-2 0,0 0 0,0-1 0,-1-1 0,0 0 0,24-13 0,-20 7 0,101-67 0,101-74 0,-95 50 0,-79 65 0,-2-4 0,-2 1 0,-2-5 0,59-79 0,-90 108 0,0 0 0,-1-1 0,-1 0 0,-1 0 0,0-1 0,-2 0 0,0 0 0,-1 0 0,-1 0 0,1-38 0,-4 50 7,0 1 0,-1-1-1,0 1 1,-1 1 0,1-2-1,-1 1 1,0 0-1,-1-1 1,0 1 0,0 1-1,0-1 1,0 0 0,-1 1-1,0 0 1,0 0 0,0 0-1,-10-7 1,2 2-219,0 2 0,-1 0 0,0 0-1,-1 0 1,0 2 0,-20-9 0,16 9-6614</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="40572.42">4447 2493 24575,'-21'54'0,"-31"179"-420,10-50-140,13 12-462,8-41 299,-1 37 723,15-114 0,-17 83 0,-24 102 0,20-106-282,4-35-88,-21 76 143,31-142 229,-33 78 2738,18 21-1878,9-68-2227,17-68-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="41085.88">3671 3243 24575,'5'2'0,"0"-1"0,-1 0 0,1 1 0,0 0 0,-1 0 0,1 0 0,-1 1 0,6 4 0,11 5 0,158 66 0,-157-69 0,0-1 0,1-1 0,0-1 0,0-2 0,30 3 0,120-1 0,-146-9 0,0-1 0,0-1 0,0 0 0,-1-2 0,0-2 0,37-17 0,58-18 0,-111 40 0,1 0 0,-1 0 0,1-2 0,-1 1 0,9-8 0,35-18 0,52-21-1365,-91 45-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="41601.46">4650 2318 24575,'-6'0'0,"1"1"0,-2-1 0,1 1 0,1 0 0,-1 0 0,1 1 0,0-1 0,0 1 0,-1 0 0,0 1 0,1 0 0,1-1 0,-1 0 0,0 2 0,1-1 0,0 2 0,-1-1 0,2 0 0,-6 6 0,-3 6 0,1 1 0,1 1 0,1-1 0,-8 23 0,14-35 0,-18 43-54,-126 325-532,95-242 446,34-89 146,-22 72 0,-51 211-6,80-291 0,-3 9 0,-10 59 0,13-52-13,7-31 231,0-1 0,-2 27-1,-8 44-77,9-67-144,1 1 0,-1 27 0,5-46 4,-1 10 0,1 0 0,0 0 0,1-1 0,0 0 0,6 23 0,-6-32 0,1 0 0,0 0 0,0 0 0,0 0 0,0-1 0,1 1 0,-1 0 0,1-1 0,0-1 0,0 1 0,0 0 0,0 0 0,1 0 0,-1 0 0,1-1 0,0 0 0,0 1 0,0-2 0,0 1 0,0 0 0,7 1 0,4 1 0,-1 0 0,1-2 0,0 1 0,0-2 0,0 0 0,1-1 0,0-1 0,-1 0 0,0-1 0,-1 0 0,24-7 0,-15 1 0,0-1 0,-1-1 0,0 0 0,-1-1 0,0-2 0,27-22 0,119-102 0,-136 107-113,100-105-1139,-118 119-5574</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="42310.97">3953 3602 24575,'-13'16'0,"-4"2"0,17-17 0,0-1 0,-1 1 0,1-1 0,0 0 0,0 1 0,0-1 0,0 1 0,0-1 0,0 1 0,1-1 0,-1 0 0,0 1 0,0-1 0,0 1 0,0-1 0,0 1 0,1-1 0,-1 0 0,0 1 0,0-1 0,0 0 0,1 1 0,-1-1 0,0 0 0,1 1 0,-1-1 0,0 0 0,1 0 0,-1 1 0,0-1 0,1 0 0,-1 0 0,1 0 0,-1 1 0,0-1 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,0 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,0 0 0,5 0 0,1 0 0,0 0 0,0 0 0,0-1 0,0 0 0,0-1 0,-1 1 0,1-1 0,-1 0 0,10-5 0,67-37 0,-64 34 0,92-52 0,216-135 0,-8-39 0,-304 225 0,-7 6 0,0-1 0,0-1 0,0 1 0,0-1 0,-1 0 0,0-1 0,10-15 0,-17 23 0,0 0 0,1 0 0,-1 0 0,0-1 0,0 1 0,0 0 0,0 0 0,0 0 0,0-1 0,0 1 0,0 0 0,0 0 0,0-1 0,0 1 0,0 0 0,0 0 0,0-1 0,0 1 0,0 0 0,0 0 0,0 0 0,0-1 0,0 1 0,0 0 0,0 0 0,0 0 0,0-1 0,-1 1 0,1 0 0,0 0 0,0 0 0,0-1 0,0 1 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,0-1 0,-1 1 0,1 0 0,0 0 0,0 0 0,-1 0 0,-13 1 0,-14 9 0,-64 41-627,3 4-1,3 5 1,-102 86-1,109-74 529,21-19-144,-95 107 0,43-6 243,90-125 85,6-9 206,1 0 1,1 0 0,1 1 0,1 1-1,0 0 1,-9 33 0,15-16 504,4-38-790,0-1 0,0 0 0,0 0-1,0 1 1,0-1 0,0 0 0,1 0 0,-1 1-1,0-1 1,0 0 0,0 0 0,0 1-1,1-1 1,-1 0 0,0 0 0,0 0 0,1 0-1,-1 1 1,0-1 0,0 0 0,1 0-1,-1 0 1,0 0 0,0 0 0,1 0 0,-1 0-1,0 0 1,0 0 0,1 0 0,-1 0-1,0 0 1,1 0 0,-1 0 0,0 0 0,0 0-1,1 0 1,-1 0 0,21-13-54,113-112 48,-85 78 0,85-67 0,0 3 0,-90 66 0,-37 35 0,1 1 0,0 1 0,16-14 0,-22 21 0,0 0 0,0-1 0,-1 1 0,1 0 0,0 0 0,-1-1 0,1 1 0,-1-1 0,0 0 0,1 1 0,-1-1 0,0 0 0,0 0 0,0 1 0,0 0 0,0-1 0,-1 0 0,1 0 0,0-4 0,-1 4 0,-1 1 0,1-1 0,0 1 0,-1-1 0,0 1 0,1 0 0,-1-1 0,0 1 0,0 0 0,0-1 0,0 1 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,-3-1 0,-11-5 0,0 0 0,-1 2 0,0 0 0,-18-3 0,10 2 0,-29-11 0,37 12 0,0-1 0,0 2 0,0 0 0,-31-3 0,-44-6 0,65 8 0,1 1 0,-32-1 0,19 3 0,-49-10 0,48 6 0,-49-1 0,54 6 0,14 0 0,0 1 0,-29 3 0,49-3 0,-1 1 0,1-1 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,-1 0 0,1 0 0,0 1 0,0-1 0,0 0 0,-1 0 0,1 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,-1 1 0,1-1 0,0 0 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,0 1 0,1-1 0,-1 0 0,0 0 0,0 1 0,0-1 0,0 0 0,0 0 0,1 0 0,-1 1 0,16 19 0,26 14 0,-24-26 0,1-1 0,-1-1 0,1 0 0,0-1 0,0-1 0,0 0 0,27 0 0,143-4 0,-85-3 0,-37 1 0,-41 0 0,1 1 0,-1 2 0,1 0 0,33 7 0,-24 8-1365,-24-5-5461</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="43212.23">3544 2365 24575,'25'1'0,"1"1"0,0 1 0,-1 1 0,1 1 0,31 11 0,13 8-110,1-4 0,1-3 0,0-1 0,0-5 0,1-3 0,86-1 0,-137-7 110,-1-2 0,0 0 0,0-1 0,0-1 0,36-12 0,254-77 0,-17-9-9,-181 69-54,-99 28 182,0 2 1,0 1-1,1 0 0,-1 1 0,0 1 0,17 1 1,-30-1-120,-1 0 0,0 0 0,1 0 0,-1 0 0,0 0 1,1 0-1,-1 0 0,0 1 0,1-1 0,-1 0 0,0 0 1,1 0-1,-1 0 0,0 0 0,1 1 0,-1-1 1,0 0-1,0 0 0,1 1 0,-1-1 0,0 0 0,0 0 1,1 1-1,-1-1 0,0 0 0,0 1 0,0-1 0,0 0 1,1 0-1,-1 1 0,0-1 0,0 0 0,0 1 1,0-1-1,0 1 0,0-1 0,0 0 0,0 2 0,0-2 1,-9 17 0,-23 17-2,30-32 1,-81 76 0,-48 49 0,17-5 0,-93 110 0,139-146 141,35-46-404,0 1 0,2 1 1,-42 82-1,58-93 310,6-12 95,0 0 1,2-1-1,0 1 0,-8 37 1,11-32-65,-5 25-54,2 2 1,0 58-1,7-64-24,-1-23 0,0 0 0,2-1 0,1 1 0,0-1 0,2 0 0,7 26 0,-9-43 0,0 1 0,0-1 0,1 0 0,0 0 0,0 0 0,0-1 0,0 1 0,0-1 0,1 1 0,-1-1 0,1 0 0,0 0 0,0-1 0,0 1 0,0-1 0,1 0 0,-1 0 0,1 0 0,-1-1 0,1 0 0,-1 0 0,9 1 0,11 1 0,-1-1 0,2-1 0,32-3 0,-27 1 0,-18 1 0,-1-1 0,1 0 0,-1 0 0,1-2 0,-1 2 0,0-2 0,0-1 0,0 0 0,0-1 0,-1 0 0,0 0 0,19-14 0,-14 10 0,1 1 0,0 0 0,17-5 0,-21 8 0,0 1 0,0-1 0,0-1 0,-1 0 0,0-1 0,0 0 0,10-9 0,-78 45 0,5 6 0,-77 69 0,-21 14 0,25-46 0,77-45 0,-111 76 0,87-56 0,59-38 0,0 1 0,1 0 0,-1 0 0,1 1 0,-12 17 0,22-26 0,0 0 0,1-1 0,-1 2 0,1-1 0,0 0 0,0 1 0,0-1 0,0 1 0,0-1 0,0 1 0,1 0 0,-1-1 0,1 1 0,0 0 0,-1-1 0,2 5 0,-1-5 0,1 0 0,0 0 0,0 0 0,0 0 0,1 0 0,-1 0 0,0 0 0,1 0 0,-1 0 0,1-1 0,0 1 0,-1-1 0,1 1 0,0-1 0,0 1 0,0-1 0,0 0 0,0 0 0,1 0 0,-1 0 0,0-1 0,4 2 0,18 5-1365,-1-4-5461</inkml:trace>
 </inkml:ink>
 </file>
 
@@ -1101,9 +1105,13 @@
   </inkml:definitions>
   <inkml:trace contextRef="#ctx0" brushRef="#br0">189 366 24575,'-1'0'0,"0"1"0,0-1 0,1 0 0,-1 1 0,0-1 0,0 0 0,0 1 0,0-1 0,0 1 0,0 0 0,1-1 0,-1 1 0,0 0 0,1-1 0,-1 1 0,0 0 0,1 0 0,-1 0 0,1-1 0,-1 1 0,1 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,-1 0 0,1 1 0,-5 32 0,4-31 0,-6 110-329,-5 41-187,0 33 59,11-134 203,-2 0 1,-2 0-1,-21 87 0,11-89 384,-8 19 417,4 2 0,3 0-1,-10 101 1,29-593-547,-5 220 0,4 171 0,1 1 0,6-29 0,-3 28 0,2-54 0,-8 42-1365,0 22-5461</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="556.39">12 267 24575,'11'-1'0,"1"0"0,-1-1 0,0 0 0,13-5 0,40-5 0,-29 10 0,13-1 0,60-10 0,-70 5 0,-1-1 0,-1-2 0,0-2 0,65-32 0,163-69 0,-250 108 0,-6 2 0,-1 1 0,0 1 0,1-1 0,0 1 0,11-1 0,-18 3 0,0 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,0 1 0,1-1 0,-1 0 0,0 1 0,1 0 0,-1-1 0,0 1 0,0 0 0,1-1 0,-1 1 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,-1 1 0,1-1 0,0 0 0,-1 0 0,1 1 0,-1-1 0,1 0 0,-1 1 0,0-1 0,1 3 0,2 23 0,-1-1 0,-1 1 0,-5 52 0,-1-1 0,4-62 0,0-1 0,-2 0 0,0 0 0,0 0 0,-2-1 0,0 1 0,0-1 0,-2 0 0,0 0 0,-10 15 0,-2-1 0,-1-1 0,-1-1 0,-39 37 0,57-60 5,-1 0 0,0-1 0,1 0 0,-1 0-1,-1 0 1,1 0 0,0-1 0,0 1 0,-1-1 0,1 0 0,0 0-1,-1-1 1,1 0 0,-1 1 0,-6-2 0,-28 6-1448,22 0-5383</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1206.61">1018 1225 24575,'1'-10'0,"1"-1"0,0 1 0,0 0 0,7-17 0,1-9 0,-9 31 0,10-44 0,24-65 0,-33 109 0,1 1 0,-1 0 0,1-1 0,0 1 0,0 0 0,0 0 0,1 1 0,0-1 0,-1 1 0,1-1 0,1 1 0,-1 0 0,0 1 0,5-3 0,11-5 0,1 2 0,22-8 0,24-9 0,-27 5-455,0 2 0,68-19 0,-90 32-6371</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1206.59">1018 1225 24575,'1'-10'0,"1"-1"0,0 1 0,0 0 0,7-17 0,1-9 0,-9 31 0,10-44 0,24-65 0,-33 109 0,1 1 0,-1 0 0,1-1 0,0 1 0,0 0 0,0 0 0,1 1 0,0-1 0,-1 1 0,1-1 0,1 1 0,-1 0 0,0 1 0,5-3 0,11-5 0,1 2 0,22-8 0,24-9 0,-27 5-455,0 2 0,68-19 0,-90 32-6371</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1700.57">2078 723 24575,'-9'0'0,"0"1"0,0 1 0,0 0 0,0 0 0,0 0 0,0 1 0,1 1 0,-1-1 0,1 1 0,0 1 0,0-1 0,0 1 0,1 1 0,0 0 0,0 0 0,0 0 0,-9 12 0,5-5 0,1 0 0,0 0 0,1 1 0,1 1 0,0 0 0,1 0 0,1 0 0,-8 28 0,4-7 0,2-4 0,-8 48 0,15-72 0,1 0 0,-1 0 0,1 0 0,1 1 0,-1-1 0,1 0 0,1 0 0,0 0 0,0 0 0,0 0 0,5 8 0,-4-12 0,0-1 0,0 0 0,0 1 0,0-2 0,1 1 0,-1 0 0,1 0 0,0-1 0,-1 0 0,1 0 0,0 0 0,1 0 0,-1-1 0,0 0 0,0 1 0,1-1 0,-1-1 0,1 1 0,-1-1 0,9 0 0,13 1 0,0-1 0,31-5 0,-50 4 0,7 0 0,1-2 0,-1 1 0,0-2 0,0 0 0,0 0 0,0-2 0,-1 1 0,0-2 0,0 0 0,0 0 0,-1-1 0,16-13 0,-26 18-151,1 1-1,-1-1 0,0 0 0,0 0 1,0 0-1,-1 0 0,1 0 1,1-6-1,2-9-6674</inkml:trace>
 </inkml:ink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1467,148 +1475,148 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="6" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="6" t="s">
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="3" t="s">
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="4"/>
-      <c r="AA1" s="5"/>
-      <c r="AB1" s="3" t="s">
+      <c r="V1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="26"/>
+      <c r="AB1" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="AC1" s="4"/>
-      <c r="AD1" s="4"/>
-      <c r="AE1" s="4"/>
-      <c r="AF1" s="4"/>
-      <c r="AG1" s="5"/>
+      <c r="AC1" s="25"/>
+      <c r="AD1" s="25"/>
+      <c r="AE1" s="25"/>
+      <c r="AF1" s="25"/>
+      <c r="AG1" s="26"/>
     </row>
     <row r="2" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="M2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="N2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Q2" s="10" t="s">
+      <c r="Q2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="R2" s="10" t="s">
+      <c r="R2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="S2" s="10" t="s">
+      <c r="S2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="11" t="s">
+      <c r="T2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="U2" s="9" t="s">
+      <c r="U2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="10" t="s">
+      <c r="V2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="12" t="s">
+      <c r="W2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="12" t="s">
+      <c r="X2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="12" t="s">
+      <c r="Y2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="Z2" s="10" t="s">
+      <c r="Z2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AA2" s="11" t="s">
+      <c r="AA2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="AB2" s="9" t="s">
+      <c r="AB2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="AC2" s="10" t="s">
+      <c r="AC2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="AD2" s="12" t="s">
+      <c r="AD2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="AE2" s="12" t="s">
+      <c r="AE2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="AF2" s="12" t="s">
+      <c r="AF2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="AG2" s="11" t="s">
+      <c r="AG2" s="7" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1713,48 +1721,26 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="13"/>
-    </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A15" s="25"/>
+      <c r="A15" s="17"/>
       <c r="B15" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A16" s="26"/>
+      <c r="A16" s="18"/>
       <c r="B16" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A17" s="27"/>
+      <c r="A17" s="19"/>
       <c r="B17" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A18" s="28"/>
+      <c r="A18" s="20"/>
       <c r="B18" s="2" t="s">
         <v>31</v>
       </c>
@@ -1777,7 +1763,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB517F82-81E6-489B-A503-EA16D9C9591F}">
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -1827,137 +1813,137 @@
       <c r="Q1" s="22"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="6" t="s">
+      <c r="B2" s="25"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="6" t="s">
+      <c r="E2" s="28"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="H2" s="8"/>
-      <c r="I2" s="3" t="s">
+      <c r="H2" s="29"/>
+      <c r="I2" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="3" t="s">
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="5"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="26"/>
     </row>
     <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="14" t="s">
+      <c r="L3" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="24" t="s">
+      <c r="O3" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="12" t="s">
+      <c r="P3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="Q3" s="15" t="s">
+      <c r="Q3" s="10" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="O4" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="P4" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q4" s="17" t="s">
+      <c r="A4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q4" s="12" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1969,51 +1955,34 @@
       <c r="P5" s="22"/>
       <c r="Q5" s="23"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-    </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="25"/>
+      <c r="A15" s="17"/>
       <c r="B15" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="26"/>
+      <c r="A16" s="18"/>
       <c r="B16" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="27"/>
+      <c r="A17" s="19"/>
       <c r="B17" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="28"/>
+      <c r="A18" s="20"/>
       <c r="B18" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
       <c r="Q19" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2031,6 +2000,145 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8596A198-0FFD-4201-AA7A-55C0B3B192CD}">
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="15.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="13.77734375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="26"/>
+    </row>
+    <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E5" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="23"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="17"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="18"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="19"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="20"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H19" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="E2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD832BE4-BC63-47C2-BD78-8A6037AEC685}">
   <dimension ref="A1:Y18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2068,102 +2176,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="6" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="6" t="s">
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="3" t="s">
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="5"/>
+      <c r="S1" s="25"/>
+      <c r="T1" s="25"/>
+      <c r="U1" s="25"/>
+      <c r="V1" s="26"/>
     </row>
     <row r="2" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="N2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="10" t="s">
+      <c r="Q2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="R2" s="9" t="s">
+      <c r="R2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="S2" s="10" t="s">
+      <c r="S2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="T2" s="12" t="s">
+      <c r="T2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="U2" s="10" t="s">
+      <c r="U2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="V2" s="11" t="s">
+      <c r="V2" s="7" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2234,16 +2342,6 @@
       <c r="V3" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
     </row>
     <row r="18" spans="25:25" x14ac:dyDescent="0.3">
       <c r="Y18" s="1" t="s">

--- a/DW/Diseño DW.xlsx
+++ b/DW/Diseño DW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uhispano-my.sharepoint.com/personal/anthony_villalobos0872_uhispano_ac_cr/Documents/Universidad/VII Cuatri/BD/Proyecto/DW/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="8_{7B331317-0294-4D6A-A2AB-5A9A270C473C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31B4CA53-E7D8-4A4A-9007-2156E02BC628}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="8_{7B331317-0294-4D6A-A2AB-5A9A270C473C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FB1B47D-F34D-4C9A-9471-8FE4B9E5B6C6}"/>
   <bookViews>
-    <workbookView xWindow="29760" yWindow="960" windowWidth="21600" windowHeight="11235" activeTab="2" xr2:uid="{4FD1E55B-BC30-4A39-93B9-D1E5AFCC1232}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{4FD1E55B-BC30-4A39-93B9-D1E5AFCC1232}"/>
   </bookViews>
   <sheets>
     <sheet name="ER" sheetId="1" r:id="rId1"/>
@@ -1105,7 +1105,7 @@
   </inkml:definitions>
   <inkml:trace contextRef="#ctx0" brushRef="#br0">189 366 24575,'-1'0'0,"0"1"0,0-1 0,1 0 0,-1 1 0,0-1 0,0 0 0,0 1 0,0-1 0,0 1 0,0 0 0,1-1 0,-1 1 0,0 0 0,1-1 0,-1 1 0,0 0 0,1 0 0,-1 0 0,1-1 0,-1 1 0,1 0 0,-1 0 0,1 0 0,0 0 0,0 0 0,-1 0 0,1 1 0,-5 32 0,4-31 0,-6 110-329,-5 41-187,0 33 59,11-134 203,-2 0 1,-2 0-1,-21 87 0,11-89 384,-8 19 417,4 2 0,3 0-1,-10 101 1,29-593-547,-5 220 0,4 171 0,1 1 0,6-29 0,-3 28 0,2-54 0,-8 42-1365,0 22-5461</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="556.39">12 267 24575,'11'-1'0,"1"0"0,-1-1 0,0 0 0,13-5 0,40-5 0,-29 10 0,13-1 0,60-10 0,-70 5 0,-1-1 0,-1-2 0,0-2 0,65-32 0,163-69 0,-250 108 0,-6 2 0,-1 1 0,0 1 0,1-1 0,0 1 0,11-1 0,-18 3 0,0 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,1 0 0,-1 0 0,0 1 0,1-1 0,-1 0 0,0 1 0,1 0 0,-1-1 0,0 1 0,0 0 0,1-1 0,-1 1 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,0 0 0,-1 1 0,1-1 0,0 0 0,-1 0 0,1 1 0,-1-1 0,1 0 0,-1 1 0,0-1 0,1 3 0,2 23 0,-1-1 0,-1 1 0,-5 52 0,-1-1 0,4-62 0,0-1 0,-2 0 0,0 0 0,0 0 0,-2-1 0,0 1 0,0-1 0,-2 0 0,0 0 0,-10 15 0,-2-1 0,-1-1 0,-1-1 0,-39 37 0,57-60 5,-1 0 0,0-1 0,1 0 0,-1 0-1,-1 0 1,1 0 0,0-1 0,0 1 0,-1-1 0,1 0 0,0 0-1,-1-1 1,1 0 0,-1 1 0,-6-2 0,-28 6-1448,22 0-5383</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1206.59">1018 1225 24575,'1'-10'0,"1"-1"0,0 1 0,0 0 0,7-17 0,1-9 0,-9 31 0,10-44 0,24-65 0,-33 109 0,1 1 0,-1 0 0,1-1 0,0 1 0,0 0 0,0 0 0,1 1 0,0-1 0,-1 1 0,1-1 0,1 1 0,-1 0 0,0 1 0,5-3 0,11-5 0,1 2 0,22-8 0,24-9 0,-27 5-455,0 2 0,68-19 0,-90 32-6371</inkml:trace>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1206.58">1018 1225 24575,'1'-10'0,"1"-1"0,0 1 0,0 0 0,7-17 0,1-9 0,-9 31 0,10-44 0,24-65 0,-33 109 0,1 1 0,-1 0 0,1-1 0,0 1 0,0 0 0,0 0 0,1 1 0,0-1 0,-1 1 0,1-1 0,1 1 0,-1 0 0,0 1 0,5-3 0,11-5 0,1 2 0,22-8 0,24-9 0,-27 5-455,0 2 0,68-19 0,-90 32-6371</inkml:trace>
   <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1700.57">2078 723 24575,'-9'0'0,"0"1"0,0 1 0,0 0 0,0 0 0,0 0 0,0 1 0,1 1 0,-1-1 0,1 1 0,0 1 0,0-1 0,0 1 0,1 1 0,0 0 0,0 0 0,0 0 0,-9 12 0,5-5 0,1 0 0,0 0 0,1 1 0,1 1 0,0 0 0,1 0 0,1 0 0,-8 28 0,4-7 0,2-4 0,-8 48 0,15-72 0,1 0 0,-1 0 0,1 0 0,1 1 0,-1-1 0,1 0 0,1 0 0,0 0 0,0 0 0,0 0 0,5 8 0,-4-12 0,0-1 0,0 0 0,0 1 0,0-2 0,1 1 0,-1 0 0,1 0 0,0-1 0,-1 0 0,1 0 0,0 0 0,1 0 0,-1-1 0,0 0 0,0 1 0,1-1 0,-1-1 0,1 1 0,-1-1 0,9 0 0,13 1 0,0-1 0,31-5 0,-50 4 0,7 0 0,1-2 0,-1 1 0,0-2 0,0 0 0,0 0 0,0-2 0,-1 1 0,0-2 0,0 0 0,0 0 0,-1-1 0,16-13 0,-26 18-151,1 1-1,-1-1 0,0 0 0,0 0 1,0 0-1,-1 0 0,1 0 1,1-6-1,2-9-6674</inkml:trace>
 </inkml:ink>
 </file>

--- a/DW/Diseño DW.xlsx
+++ b/DW/Diseño DW.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="69" documentId="8_{7B331317-0294-4D6A-A2AB-5A9A270C473C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FB1B47D-F34D-4C9A-9471-8FE4B9E5B6C6}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{4FD1E55B-BC30-4A39-93B9-D1E5AFCC1232}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{4FD1E55B-BC30-4A39-93B9-D1E5AFCC1232}"/>
   </bookViews>
   <sheets>
     <sheet name="ER" sheetId="1" r:id="rId1"/>
